--- a/program_mapping.xlsx
+++ b/program_mapping.xlsx
@@ -218,7 +218,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="270"/>
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
